--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3430" uniqueCount="344">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -529,10 +529,13 @@
     <t>Section.id</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Identifiant de la section</t>
+  </si>
+  <si>
     <t>Section.code</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CE
@@ -4714,7 +4717,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>166</v>
       </c>
@@ -4733,7 +4736,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4744,8 +4747,12 @@
       <c r="K33" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
+      <c r="L33" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4815,10 +4822,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4832,7 +4839,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4841,13 +4848,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4898,7 +4905,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4918,10 +4925,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5017,12 +5024,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5032,13 +5039,13 @@
         <v>62</v>
       </c>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>74</v>
@@ -5051,7 +5058,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5063,7 +5070,7 @@
         <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>74</v>
@@ -5102,7 +5109,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5120,28 +5127,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5154,7 +5161,7 @@
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5166,7 +5173,7 @@
         <v>74</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>74</v>
@@ -5205,7 +5212,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5225,17 +5232,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5257,7 +5264,7 @@
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5269,7 +5276,7 @@
         <v>74</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>74</v>
@@ -5308,7 +5315,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5328,17 +5335,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5360,7 +5367,7 @@
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5411,7 +5418,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5429,28 +5436,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5463,7 +5470,7 @@
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5475,7 +5482,7 @@
         <v>74</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>74</v>
@@ -5514,7 +5521,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5534,10 +5541,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5560,11 +5567,11 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5615,7 +5622,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5635,10 +5642,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5665,7 +5672,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5716,7 +5723,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5736,17 +5743,17 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>80</v>
@@ -5764,11 +5771,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5819,7 +5826,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5839,17 +5846,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
@@ -5867,11 +5874,11 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5922,7 +5929,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5942,17 +5949,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
@@ -5970,11 +5977,11 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6025,7 +6032,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6045,10 +6052,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6062,7 +6069,7 @@
         <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>74</v>
@@ -6071,13 +6078,13 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6128,7 +6135,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6148,10 +6155,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6165,7 +6172,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6174,13 +6181,13 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6231,7 +6238,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6251,10 +6258,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6277,7 +6284,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6330,7 +6337,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6350,10 +6357,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6409,25 +6416,25 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -6447,10 +6454,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6473,7 +6480,7 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6526,7 +6533,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6546,10 +6553,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6572,7 +6579,7 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
@@ -6625,7 +6632,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6645,10 +6652,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6671,7 +6678,7 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
@@ -6724,7 +6731,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6744,10 +6751,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6761,7 +6768,7 @@
         <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6770,7 +6777,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6811,7 +6818,7 @@
         <v>74</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -6821,7 +6828,7 @@
         <v>124</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6841,13 +6848,13 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>74</v>
@@ -6869,7 +6876,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6922,7 +6929,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6942,10 +6949,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7043,10 +7050,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7144,10 +7151,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7245,10 +7252,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7346,10 +7353,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7449,10 +7456,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7552,10 +7559,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7655,10 +7662,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7758,10 +7765,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7859,10 +7866,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7892,7 +7899,7 @@
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
@@ -7918,7 +7925,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>74</v>
@@ -7936,7 +7943,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7956,10 +7963,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7993,7 +8000,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>74</v>
@@ -8035,7 +8042,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8055,10 +8062,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8081,7 +8088,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8134,7 +8141,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8154,10 +8161,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8180,7 +8187,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8233,7 +8240,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8253,10 +8260,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8279,10 +8286,10 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
@@ -8334,7 +8341,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8354,10 +8361,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8380,7 +8387,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8433,7 +8440,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8453,10 +8460,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8479,7 +8486,7 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
@@ -8532,7 +8539,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -8552,10 +8559,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8578,7 +8585,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -8631,7 +8638,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -8651,10 +8658,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8677,7 +8684,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8730,7 +8737,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8750,10 +8757,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8776,7 +8783,7 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8829,7 +8836,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8849,10 +8856,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8875,7 +8882,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8928,7 +8935,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8948,13 +8955,13 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>74</v>
@@ -8976,7 +8983,7 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
@@ -9029,7 +9036,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9049,13 +9056,13 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>74</v>
@@ -9077,7 +9084,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9130,7 +9137,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9150,10 +9157,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9251,10 +9258,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9352,10 +9359,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9453,10 +9460,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9554,10 +9561,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9657,10 +9664,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9760,10 +9767,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9863,10 +9870,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9966,10 +9973,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10067,10 +10074,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10100,7 +10107,7 @@
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
@@ -10126,7 +10133,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10144,7 +10151,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10164,10 +10171,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10201,7 +10208,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>74</v>
@@ -10243,7 +10250,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10263,10 +10270,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10289,7 +10296,7 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10342,7 +10349,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10362,10 +10369,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10388,7 +10395,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10441,7 +10448,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10461,10 +10468,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10487,10 +10494,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -10542,7 +10549,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10562,10 +10569,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10588,7 +10595,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10641,7 +10648,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10661,10 +10668,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10687,7 +10694,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10740,7 +10747,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10760,10 +10767,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10786,7 +10793,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10839,7 +10846,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10859,10 +10866,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10885,7 +10892,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -10938,7 +10945,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10958,10 +10965,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10984,7 +10991,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11037,7 +11044,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11057,10 +11064,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11083,7 +11090,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11136,7 +11143,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11156,10 +11163,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11182,7 +11189,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11235,7 +11242,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11255,10 +11262,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11356,10 +11363,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11457,10 +11464,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11558,10 +11565,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11659,10 +11666,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11762,10 +11769,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11865,10 +11872,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -11968,10 +11975,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12071,10 +12078,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12172,10 +12179,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12202,7 +12209,7 @@
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12211,7 +12218,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>74</v>
@@ -12253,7 +12260,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12273,10 +12280,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12310,7 +12317,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>74</v>
@@ -12352,7 +12359,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12372,10 +12379,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12398,7 +12405,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12451,7 +12458,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
